--- a/Excel/05Lookup_Functions.xlsx
+++ b/Excel/05Lookup_Functions.xlsx
@@ -5,25 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\FOI_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\FOI_4\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15999B-AFE2-44FB-8B66-5730E539A611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644FFD1F-8AB1-441A-B777-EA4BB2598B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VLOOKUP_Basics" sheetId="1" r:id="rId1"/>
-    <sheet name="HLOOKUP_Basics" sheetId="2" r:id="rId2"/>
-    <sheet name="XLOOKUP_Basics" sheetId="3" r:id="rId3"/>
-    <sheet name="Another" sheetId="7" r:id="rId4"/>
-    <sheet name="Challenge_Tasks" sheetId="6" r:id="rId5"/>
-    <sheet name="Task" sheetId="9" r:id="rId6"/>
-    <sheet name="Index match" sheetId="10" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId8"/>
+    <sheet name="Ref" sheetId="13" r:id="rId1"/>
+    <sheet name="VLOOKUP_Basics" sheetId="1" r:id="rId2"/>
+    <sheet name="HLOOKUP_Basics" sheetId="2" r:id="rId3"/>
+    <sheet name="XLOOKUP_Basics" sheetId="3" r:id="rId4"/>
+    <sheet name="Another" sheetId="7" r:id="rId5"/>
+    <sheet name="Challenge_Tasks" sheetId="6" r:id="rId6"/>
+    <sheet name="Task" sheetId="9" r:id="rId7"/>
+    <sheet name="Index match" sheetId="10" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XLOOKUP_Basics!$A$1:$A$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XLOOKUP_Basics!$A$1:$A$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="77">
   <si>
     <t>ProductID</t>
   </si>
@@ -265,6 +288,15 @@
   </si>
   <si>
     <t>Bonus Amount</t>
+  </si>
+  <si>
+    <t>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:B10),0)</t>
+  </si>
+  <si>
+    <t>HLOOKUP($F$5,$A$1:$E$3,2,0)</t>
+  </si>
+  <si>
+    <t>XLOOKUP(A9,A2:A5,B2:E5)</t>
   </si>
 </sst>
 </file>
@@ -329,7 +361,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,6 +401,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -514,6 +552,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -853,6 +897,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5234BF-CD7C-4C0D-97F7-B461D8BF5EFD}">
+  <dimension ref="B2:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <f>C2+$F$2</f>
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D6" si="0">C3+$F$2</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <f>C5+$F$2</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f>SUM(B2:B6)</f>
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C2:C6)</f>
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <f>C7+$F$2</f>
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -953,7 +1084,10 @@
       <c r="G5" s="7">
         <v>102</v>
       </c>
-      <c r="H5" s="9"/>
+      <c r="H5" s="9">
+        <f>VLOOKUP(G5,A1:D5,3,0)</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -1009,20 +1143,34 @@
         <v>3</v>
       </c>
       <c r="G10" s="7">
-        <v>107</v>
-      </c>
-      <c r="H10" s="7"/>
+        <v>108</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f>IFERROR(VLOOKUP(G10,A1:D5,4,0), "Not found")</f>
+        <v>Not found</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>104</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="9" t="str">
+        <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:B10),0)</f>
+        <v>Marker</v>
+      </c>
+      <c r="C11" s="9">
+        <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:C10),0)</f>
+        <v>15</v>
+      </c>
+      <c r="D11" s="9" t="str">
+        <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:D10),0)</f>
+        <v>Stationery</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="28" t="s">
+        <v>74</v>
+      </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
@@ -1035,7 +1183,7 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 A11" xr:uid="{A2A1B387-306C-4132-8C5A-FAB70B00FB3B}">
       <formula1>$A$2:$A$5</formula1>
     </dataValidation>
@@ -1044,7 +1192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1126,8 +1274,14 @@
       <c r="F5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="7">
+        <f>HLOOKUP($F$5,$A$1:$E$3,2,0)</f>
+        <v>800</v>
+      </c>
+      <c r="H5" s="7">
+        <f>HLOOKUP($F$5,$A$1:$E$3,3,0)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
@@ -1136,7 +1290,9 @@
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="31" t="s">
+        <v>75</v>
+      </c>
       <c r="G7" s="31"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
@@ -1189,7 +1345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1286,7 +1442,10 @@
       <c r="G4" s="7">
         <v>208</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="33" t="str">
+        <f>_xlfn.XLOOKUP(G4,A2:A5,B2:B5, "Not found")</f>
+        <v>Not found</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -1344,16 +1503,28 @@
       <c r="G8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="7">
+        <f>_xlfn.XLOOKUP(G8,B2:B5,D2:D5, "Not found")</f>
+        <v>55000</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>201</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="B9" s="7" t="str" cm="1">
+        <f t="array" ref="B9:E9">_xlfn.XLOOKUP(A9,A2:A5,B2:E5)</f>
+        <v>Alice</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <v>HR</v>
+      </c>
+      <c r="D9" s="8">
+        <v>50000</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <v>2023-01-10</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G10" s="27"/>
@@ -1361,6 +1532,11 @@
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
@@ -1369,18 +1545,19 @@
       <c r="H12" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G10:I10"/>
+    <mergeCell ref="A11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E188AE37-C942-44D9-AFA8-62ABDC05D4D0}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1416,7 +1593,10 @@
       <c r="A3" s="7">
         <v>103</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="22" t="str">
+        <f>VLOOKUP(A3,VLOOKUP_Basics!A1:D5,2,0)</f>
+        <v>Eraser</v>
+      </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
@@ -1429,7 +1609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1522,7 +1702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD803EC-73F3-4807-A24B-D5D650856789}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1808,7 +1988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B102B2-F93F-4FE6-AA26-382ABB013726}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1914,7 +2094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B91139-A8A4-4BEA-A5AA-24C51D114EBB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
